--- a/output/pdf_financials_xlsx/QURI.xlsx
+++ b/output/pdf_financials_xlsx/QURI.xlsx
@@ -3755,16 +3755,16 @@
         <v>0</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.024643</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.024643</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.024643</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.045944</v>
       </c>
     </row>
     <row r="93">
@@ -5854,7 +5854,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/QURI.xlsx
+++ b/output/pdf_financials_xlsx/QURI.xlsx
@@ -714,25 +714,25 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.025812</v>
+        <v>0.029312</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.169559</v>
+        <v>0.571368</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.096274</v>
+        <v>0.16293</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.179596</v>
+        <v>0.346661</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.376404</v>
+        <v>0.51534</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.369818</v>
+        <v>0.408123</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.380874</v>
+        <v>0.437202</v>
       </c>
     </row>
     <row r="11">
@@ -747,25 +747,25 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.025812</v>
+        <v>-0.029312</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.169559</v>
+        <v>-0.571368</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.096274</v>
+        <v>-0.16293</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.179596</v>
+        <v>-0.346661</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.376404</v>
+        <v>-0.51534</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.369818</v>
+        <v>-0.408123</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.380874</v>
+        <v>-0.437202</v>
       </c>
     </row>
     <row r="12">
@@ -1556,19 +1556,19 @@
         </is>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.586063</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.596115</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.214792</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.01046</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>1.212333</v>
       </c>
     </row>
     <row r="35">
@@ -1630,19 +1630,19 @@
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.586063</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.596115</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.214792</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.01046</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>1.212333</v>
       </c>
     </row>
     <row r="37">
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.595063</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.731722</v>
+        <v>0.135607</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0</v>
@@ -5384,7 +5384,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -6228,7 +6228,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -9334,7 +9334,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -9343,25 +9343,25 @@
         </is>
       </c>
       <c r="F75" s="5" t="n">
-        <v>-0.029312</v>
+        <v>0.029312</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>-0.571368</v>
+        <v>0.571368</v>
       </c>
       <c r="H75" s="5" t="n">
-        <v>-0.16293</v>
+        <v>0.16293</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>-0.346661</v>
+        <v>0.346661</v>
       </c>
       <c r="J75" s="5" t="n">
-        <v>-0.51534</v>
+        <v>0.51534</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>-0.408123</v>
+        <v>0.408123</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>-0.437202</v>
+        <v>0.437202</v>
       </c>
     </row>
     <row r="76">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">

--- a/output/pdf_financials_xlsx/QURI.xlsx
+++ b/output/pdf_financials_xlsx/QURI.xlsx
@@ -463,12 +463,12 @@
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>2018-11</t>
+          <t>2018-10</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>2019-11</t>
+          <t>2019-10</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
@@ -1545,15 +1545,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>0.027371</v>
       </c>
       <c r="E34" s="3" t="n">
         <v>0.586063</v>
@@ -1582,15 +1578,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E35" s="3" t="n">
         <v>0</v>
@@ -1619,15 +1611,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>0.027371</v>
       </c>
       <c r="E36" s="3" t="n">
         <v>0.586063</v>
@@ -1656,15 +1644,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E37" s="3" t="n">
         <v>0</v>
@@ -1693,15 +1677,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E38" s="3" t="n">
         <v>0</v>
@@ -1730,15 +1710,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E39" s="3" t="n">
         <v>0</v>
@@ -1767,15 +1743,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C40" s="3" t="n">
+        <v>0.000852</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>0.032692</v>
       </c>
       <c r="E40" s="3" t="n">
         <v>0.00332</v>
@@ -1804,15 +1776,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C41" s="3" t="n">
+        <v>0.000852</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>0.032692</v>
       </c>
       <c r="E41" s="3" t="n">
         <v>0.00332</v>
@@ -1841,15 +1809,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E42" s="3" t="n">
         <v>0</v>
@@ -1878,15 +1842,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E43" s="3" t="n">
         <v>0</v>
@@ -1915,15 +1875,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E44" s="3" t="n">
         <v>0</v>
@@ -1952,15 +1908,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E45" s="3" t="n">
         <v>0</v>
@@ -1989,15 +1941,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E46" s="3" t="n">
         <v>0</v>
@@ -2026,15 +1974,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E47" s="3" t="n">
         <v>0</v>
@@ -2063,15 +2007,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
         <v>0.008999999999999999</v>
@@ -2143,15 +2083,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E50" s="3" t="n">
         <v>0</v>
@@ -2180,15 +2116,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E51" s="3" t="n">
         <v>0</v>
@@ -2217,15 +2149,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E52" s="3" t="n">
         <v>0</v>
@@ -2254,15 +2182,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E53" s="3" t="n">
         <v>0</v>
@@ -2291,15 +2215,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E54" s="3" t="n">
         <v>0</v>
@@ -2375,15 +2295,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E56" s="3" t="n">
         <v>0</v>
@@ -2412,15 +2328,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E57" s="3" t="n">
         <v>0</v>
@@ -2449,15 +2361,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E58" s="3" t="n">
         <v>0.860994</v>
@@ -2486,15 +2394,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E59" s="3" t="n">
         <v>0</v>
@@ -2523,15 +2427,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E60" s="3" t="n">
         <v>0</v>
@@ -2560,15 +2460,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E61" s="3" t="n">
         <v>0.084842</v>
@@ -2640,15 +2536,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C63" s="3" t="n">
+        <v>0.001852</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>0.09381299999999999</v>
       </c>
       <c r="E63" s="3" t="n">
         <v>1.544219</v>
@@ -2677,21 +2569,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C64" s="3" t="n">
+        <v>0.023914</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>0.389215</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>0.258874</v>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0</v>
+        <v>0.282124</v>
       </c>
       <c r="G64" s="3" t="n">
         <v>0</v>
@@ -2714,15 +2602,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E65" s="3" t="n">
         <v>0</v>
@@ -2751,15 +2635,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E66" s="3" t="n">
         <v>0</v>
@@ -2788,30 +2668,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0.015</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.03532</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.030568</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.058136</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.07325</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.1354</v>
       </c>
     </row>
     <row r="68">
@@ -2825,15 +2701,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C68" s="3" t="n">
+        <v>0.023914</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>0.389215</v>
       </c>
       <c r="E68" s="3" t="n">
         <v>0.5066310000000001</v>
@@ -2862,15 +2734,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>0.180422</v>
       </c>
       <c r="E69" s="3" t="n">
         <v>0.180422</v>
@@ -2899,15 +2767,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E70" s="3" t="n">
         <v>0</v>
@@ -2936,15 +2800,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>0.180422</v>
       </c>
       <c r="E71" s="3" t="n">
         <v>0.180422</v>
@@ -2973,15 +2833,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E72" s="3" t="n">
         <v>0</v>
@@ -3010,15 +2866,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E73" s="3" t="n">
         <v>0</v>
@@ -3047,15 +2899,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E74" s="3" t="n">
         <v>0</v>
@@ -3084,15 +2932,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E75" s="3" t="n">
         <v>0</v>
@@ -3168,15 +3012,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E77" s="3" t="n">
         <v>0</v>
@@ -3205,15 +3045,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E78" s="3" t="n">
         <v>0</v>
@@ -3242,15 +3078,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E79" s="3" t="n">
         <v>0</v>
@@ -3284,10 +3116,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D80" s="3" t="n">
+        <v>-0.3791780154006523</v>
       </c>
       <c r="E80" s="3" t="n">
         <v>0.2104866501937781</v>
@@ -3324,15 +3154,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E81" s="3" t="n">
         <v>0</v>
@@ -3361,15 +3187,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E82" s="3" t="n">
         <v>0</v>
@@ -3398,15 +3220,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E83" s="3" t="n">
         <v>0</v>
@@ -3435,15 +3253,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E84" s="3" t="n">
         <v>0</v>
@@ -3472,15 +3286,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E85" s="3" t="n">
         <v>0</v>
@@ -3556,15 +3366,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C87" s="3" t="n">
+        <v>0.023914</v>
+      </c>
+      <c r="D87" s="3" t="n">
+        <v>0.5696369999999999</v>
       </c>
       <c r="E87" s="3" t="n">
         <v>0.687053</v>
@@ -3593,15 +3399,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C88" s="3" t="n">
+        <v>0.00725</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>0.312736</v>
       </c>
       <c r="E88" s="3" t="n">
         <v>1.965927</v>
@@ -3630,15 +3432,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E89" s="3" t="n">
         <v>0</v>
@@ -3667,15 +3465,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C90" s="3" t="n">
+        <v>-0.029312</v>
+      </c>
+      <c r="D90" s="3" t="n">
+        <v>-0.78856</v>
       </c>
       <c r="E90" s="3" t="n">
         <v>-1.108761</v>
@@ -3704,15 +3498,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E91" s="3" t="n">
         <v>0</v>
@@ -3741,15 +3531,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E92" s="3" t="n">
         <v>0</v>
@@ -3778,15 +3564,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E93" s="3" t="n">
         <v>0</v>
@@ -3815,15 +3597,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C94" s="3" t="n">
+        <v>-0.022062</v>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>-0.475824</v>
       </c>
       <c r="E94" s="3" t="n">
         <v>0.857166</v>
@@ -3852,15 +3630,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="E95" s="3" t="n">
         <v>0</v>
@@ -3889,15 +3663,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C96" s="3" t="n">
+        <v>-0.022062</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>-0.475824</v>
       </c>
       <c r="E96" s="3" t="n">
         <v>0.857166</v>
@@ -3926,15 +3696,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C97" s="3" t="n">
+        <v>-11.91252699784017</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>-5.072047584023537</v>
       </c>
       <c r="E97" s="3" t="n">
         <v>0.5550805941385257</v>
@@ -4038,28 +3804,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C101" s="3" t="n">
+        <v>-0.000852</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.02469</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>0.004462</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>-0.01082</v>
       </c>
       <c r="G101" s="3" t="n">
-        <v>0</v>
+        <v>0.003493</v>
       </c>
       <c r="H101" s="3" t="n">
-        <v>0</v>
+        <v>0.005868</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0</v>
+        <v>0.001059</v>
       </c>
     </row>
     <row r="102">
@@ -4212,25 +3976,25 @@
         </is>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.030164</v>
+        <v>0.029312</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.524084</v>
+        <v>0.499394</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.033358</v>
+        <v>0.03782</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>-0.105581</v>
+        <v>-0.116401</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.139524</v>
+        <v>0.143017</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0.197923</v>
+        <v>0.203791</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0.252542</v>
+        <v>0.253601</v>
       </c>
     </row>
     <row r="107">
@@ -5299,7 +5063,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L135"/>
+  <dimension ref="A1:L143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5397,10 +5161,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G2" s="5" t="n">
+        <v>0.027371</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -5442,15 +5204,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F3" s="5" t="n">
+        <v>0.000852</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>0.032692</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -5497,10 +5255,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G4" s="5" t="n">
+        <v>0.03375</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -5754,15 +5510,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F9" s="5" t="n">
+        <v>0.023914</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0.5696369999999999</v>
       </c>
       <c r="H9" s="5" t="n">
         <v>0.687053</v>
@@ -6615,13 +6367,13 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>October 31, 2025 October</t>
+          <t>Due from related party 8</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -6630,10 +6382,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F25" s="5" t="n">
+        <v>0.001</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -6655,32 +6405,32 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K25" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="L25" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Operating activities</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Net loss $</t>
+          <t>Total Assets $</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
+          <t>TotalAssets</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -6689,58 +6439,64 @@
         </is>
       </c>
       <c r="F26" s="5" t="n">
-        <v>-0.029312</v>
+        <v>0.001852</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.759248</v>
-      </c>
-      <c r="H26" s="5" t="n">
-        <v>-0.16908</v>
-      </c>
-      <c r="I26" s="5" t="n">
-        <v>-0.346661</v>
-      </c>
-      <c r="J26" s="5" t="n">
-        <v>-0.51534</v>
-      </c>
-      <c r="K26" s="5" t="n">
-        <v>-0.408123</v>
-      </c>
-      <c r="L26" s="5" t="n">
-        <v>-0.216766</v>
+        <v>0.09381299999999999</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Items not affecting cash</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Gain on forgiveness of debts</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities 5 $</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F27" s="5" t="n">
+        <v>0.023914</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0.389215</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -6762,73 +6518,87 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L27" s="5" t="n">
-        <v>-0.220436</v>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Changes in non-cash working capital items</t>
-        </is>
-      </c>
+          <t>balance_sheet</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GST receivable</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>Loans payable 6</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F28" s="5" t="n">
-        <v>-0.000852</v>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.02469</v>
-      </c>
-      <c r="H28" s="5" t="n">
-        <v>0.004462</v>
-      </c>
-      <c r="I28" s="5" t="n">
-        <v>-0.01082</v>
-      </c>
-      <c r="J28" s="5" t="n">
-        <v>0.003493</v>
-      </c>
-      <c r="K28" s="5" t="n">
-        <v>0.005868</v>
-      </c>
-      <c r="L28" s="5" t="n">
-        <v>0.001059</v>
+        <v>0.180422</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Shareholders' Deficiency</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Prepaid expenses and deposits</t>
+          <t>Share capital 7</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
+          <t>CapitalStock</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -6836,53 +6606,57 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F29" s="5" t="n">
+        <v>0.00725</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0.312736</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I29" s="5" t="n">
-        <v>-0.126607</v>
-      </c>
-      <c r="J29" s="5" t="n">
-        <v>0.048425</v>
-      </c>
-      <c r="K29" s="5" t="n">
-        <v>-0.002533</v>
-      </c>
-      <c r="L29" s="5" t="n">
-        <v>0.0026</v>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Shareholders' Deficiency</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
+          <t>Deficit</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>RetainedEarnings</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -6891,46 +6665,56 @@
         </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.030164</v>
+        <v>-0.029312</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.524084</v>
-      </c>
-      <c r="H30" s="5" t="n">
-        <v>0.033358</v>
-      </c>
-      <c r="I30" s="5" t="n">
-        <v>0.021026</v>
-      </c>
-      <c r="J30" s="5" t="n">
-        <v>0.091099</v>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>0.200456</v>
-      </c>
-      <c r="L30" s="5" t="n">
-        <v>0.249942</v>
+        <v>-0.78856</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Shareholders' Deficiency</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Net cash flows used in operating activities</t>
+          <t>Total Shareholders' Deficiency</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
+          <t>StockholdersEquity</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -6938,67 +6722,79 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F31" s="5" t="n">
+        <v>-0.022062</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.071974</v>
-      </c>
-      <c r="H31" s="5" t="n">
-        <v>-0.13126</v>
-      </c>
-      <c r="I31" s="5" t="n">
-        <v>-0.463062</v>
-      </c>
-      <c r="J31" s="5" t="n">
-        <v>-0.372323</v>
-      </c>
-      <c r="K31" s="5" t="n">
-        <v>-0.204332</v>
-      </c>
-      <c r="L31" s="5" t="n">
-        <v>-0.183601</v>
+        <v>-0.475824</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Shareholders' Deficiency</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Shares issued for cash</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
+          <t>Total Liabilities and Shareholders' Deficiency $</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H32" s="5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I32" s="5" t="n">
-        <v>0.65</v>
+      <c r="F32" s="5" t="n">
+        <v>0.001852</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0.09381299999999999</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -7010,8 +6806,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L32" s="5" t="n">
-        <v>1.412836</v>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -7020,21 +6818,13 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Financing activities</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Share issuance costs</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>NetOtherFinancingCharges</t>
-        </is>
-      </c>
+          <t>October 31, 2025 October</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -7050,24 +6840,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H33" s="5" t="n">
-        <v>-0.00519</v>
-      </c>
-      <c r="I33" s="5" t="n">
-        <v>-0.173949</v>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K33" s="5" t="n">
+        <v>0.002024</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>-0.027362</v>
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="34">
@@ -7078,17 +6870,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Operating activities</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Net cash flows provided by financing activities</t>
+          <t>Net loss $</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -7096,36 +6888,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F34" s="5" t="n">
+        <v>-0.029312</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.119559</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.759248</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>-0.16908</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>-0.346661</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>-0.51534</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>-0.408123</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>1.385474</v>
+        <v>-0.216766</v>
       </c>
     </row>
     <row r="35">
@@ -7136,19 +6918,15 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Net change in cash</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Gain on forgiveness of debts</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -7159,23 +6937,33 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G35" s="5" t="n">
-        <v>0.027371</v>
-      </c>
-      <c r="H35" s="5" t="n">
-        <v>-0.262181</v>
-      </c>
-      <c r="I35" s="5" t="n">
-        <v>0.010052</v>
-      </c>
-      <c r="J35" s="5" t="n">
-        <v>-0.381323</v>
-      </c>
-      <c r="K35" s="5" t="n">
-        <v>-0.204332</v>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L35" s="5" t="n">
-        <v>1.201873</v>
+        <v>-0.220436</v>
       </c>
     </row>
     <row r="36">
@@ -7186,44 +6974,44 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cash, beginning</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
+          <t>GST receivable</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F36" s="5" t="n">
+        <v>-0.000852</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>-0.02469</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>0.848244</v>
+        <v>0.004462</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>0.586063</v>
+        <v>-0.01082</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>0.596115</v>
+        <v>0.003493</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>0.214792</v>
+        <v>0.005868</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>0.01046</v>
+        <v>0.001059</v>
       </c>
     </row>
     <row r="37">
@@ -7234,15 +7022,19 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cash, ending $</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>Prepaid expenses and deposits</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -7253,23 +7045,27 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G37" s="5" t="n">
-        <v>0.027371</v>
-      </c>
-      <c r="H37" s="5" t="n">
-        <v>0.586063</v>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I37" s="5" t="n">
-        <v>0.596115</v>
+        <v>-0.126607</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>0.214792</v>
+        <v>0.048425</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>0.01046</v>
+        <v>-0.002533</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>1.212333</v>
+        <v>0.0026</v>
       </c>
     </row>
     <row r="38">
@@ -7280,54 +7076,44 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cash paid during the year for interest $</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F38" s="5" t="n">
+        <v>0.030164</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0.524084</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>0.033358</v>
+      </c>
+      <c r="I38" s="5" t="n">
+        <v>0.021026</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>0.091099</v>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>0.200456</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>0.249942</v>
       </c>
     </row>
     <row r="39">
@@ -7338,15 +7124,19 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cash paid during the year for income taxes $</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>Net cash flows used in operating activities</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
@@ -7357,35 +7147,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G39" s="5" t="n">
+        <v>-0.071974</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>-0.13126</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>-0.463062</v>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>-0.372323</v>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>-0.204332</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>-0.183601</v>
       </c>
     </row>
     <row r="40">
@@ -7396,15 +7174,19 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Non cash transactions</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Common shares issued for debt settlement $</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>Shares issued for cash</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E40" t="inlineStr">
         <is>
           <t>-</t>
@@ -7420,13 +7202,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H40" s="5" t="n">
+        <v>0.04</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>0.180422</v>
+        <v>0.65</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -7439,7 +7219,7 @@
         </is>
       </c>
       <c r="L40" s="5" t="n">
-        <v>0.095</v>
+        <v>1.412836</v>
       </c>
     </row>
     <row r="41">
@@ -7450,15 +7230,19 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Non cash transactions</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Finder warrants $</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>Share issuance costs</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -7474,15 +7258,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H41" s="5" t="n">
+        <v>-0.00519</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>-0.173949</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -7495,7 +7275,7 @@
         </is>
       </c>
       <c r="L41" s="5" t="n">
-        <v>0.021301</v>
+        <v>-0.027362</v>
       </c>
     </row>
     <row r="42">
@@ -7504,13 +7284,21 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Financing activities</t>
+        </is>
+      </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>October 31, 2024 October</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
+          <t>Net cash flows provided by financing activities</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -7521,10 +7309,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G42" s="5" t="n">
+        <v>0.119559</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -7536,16 +7322,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J42" s="5" t="n">
-        <v>0.002023</v>
-      </c>
-      <c r="K42" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>1.385474</v>
       </c>
     </row>
     <row r="43">
@@ -7556,15 +7344,19 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Exploration expenditures</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>Net change in cash</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -7576,26 +7368,22 @@
         </is>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.027295</v>
+        <v>0.027371</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>-0.085976</v>
+        <v>-0.262181</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>-0.002937</v>
+        <v>0.010052</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>-0.008999999999999999</v>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.381323</v>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>-0.204332</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>1.201873</v>
       </c>
     </row>
     <row r="44">
@@ -7606,19 +7394,15 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Net cash flows used in investing activities</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
+          <t>Cash, beginning</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>-</t>
@@ -7629,27 +7413,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G44" s="5" t="n">
-        <v>-0.020214</v>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H44" s="5" t="n">
-        <v>-0.085976</v>
+        <v>0.848244</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>-0.002937</v>
+        <v>0.586063</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>-0.008999999999999999</v>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.596115</v>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>0.214792</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>0.01046</v>
       </c>
     </row>
     <row r="45">
@@ -7660,19 +7442,15 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Net change in cash</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Cash, ending $</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>-</t>
@@ -7683,31 +7461,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G45" s="5" t="n">
+        <v>0.027371</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>0.586063</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>0.596115</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>-0.381323</v>
+        <v>0.214792</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>-0.204332</v>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.01046</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>1.212333</v>
       </c>
     </row>
     <row r="46">
@@ -7718,12 +7488,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cash, beginning</t>
+          <t>Cash paid during the year for interest $</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -7752,11 +7522,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J46" s="5" t="n">
-        <v>0.596115</v>
-      </c>
-      <c r="K46" s="5" t="n">
-        <v>0.214792</v>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -7772,12 +7546,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cash, ending $</t>
+          <t>Cash paid during the year for income taxes $</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
@@ -7806,11 +7580,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J47" s="5" t="n">
-        <v>0.214792</v>
-      </c>
-      <c r="K47" s="5" t="n">
-        <v>0.01046</v>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -7826,12 +7604,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Non cash transactions</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cash paid during the period for interest $</t>
+          <t>Common shares issued for debt settlement $</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
@@ -7855,10 +7633,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I48" s="5" t="n">
+        <v>0.180422</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -7870,10 +7646,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L48" s="5" t="n">
+        <v>0.095</v>
       </c>
     </row>
     <row r="49">
@@ -7884,12 +7658,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Non cash transactions</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cash paid during the period for income taxes $</t>
+          <t>Finder warrants $</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -7928,10 +7702,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L49" s="5" t="n">
+        <v>0.021301</v>
       </c>
     </row>
     <row r="50">
@@ -7943,7 +7715,7 @@
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>October 31, 2023 October</t>
+          <t>October 31, 2024 October</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
@@ -7967,16 +7739,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I50" s="5" t="n">
-        <v>0.002022</v>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J50" s="5" t="n">
+        <v>0.002023</v>
+      </c>
+      <c r="K50" s="5" t="n">
         <v>3.1e-05</v>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -7992,19 +7764,15 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Net cash flows used in financing activities</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Exploration expenditures</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -8015,23 +7783,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G51" s="5" t="n">
+        <v>-0.027295</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>-0.085976</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>0.476051</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.002937</v>
+      </c>
+      <c r="J51" s="5" t="n">
+        <v>-0.008999999999999999</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -8052,15 +7814,19 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Non cash transactions</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Share issued for property $</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
+          <t>Net cash flows used in investing activities</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -8071,23 +7837,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G52" s="5" t="n">
+        <v>-0.020214</v>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>-0.085976</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.002937</v>
+      </c>
+      <c r="J52" s="5" t="n">
+        <v>-0.008999999999999999</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -8108,15 +7868,19 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Non cash transactions</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Cash paid during the year for interest $</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr"/>
+          <t>Net change in cash</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E53" t="inlineStr">
         <is>
           <t>-</t>
@@ -8142,15 +7906,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J53" s="5" t="n">
+        <v>-0.381323</v>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>-0.204332</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -8166,12 +7926,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Non cash transactions</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Cash paid during the year for income taxes $</t>
+          <t>Cash, beginning</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
@@ -8200,15 +7960,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J54" s="5" t="n">
+        <v>0.596115</v>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>0.214792</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -8224,19 +7980,15 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Prepaid expenses and deposit</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>ChangeInPrepaidAssets</t>
-        </is>
-      </c>
+          <t>Cash, ending $</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -8257,18 +8009,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I55" s="5" t="n">
-        <v>-0.126607</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="n">
+        <v>0.214792</v>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>0.01046</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -8284,12 +8034,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Deferred financing fees</t>
+          <t>Cash paid during the period for interest $</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
@@ -8308,8 +8058,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H56" s="5" t="n">
-        <v>-0.07975500000000001</v>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -8340,19 +8092,15 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Net cash flows provided by (used in) financing activities</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Cash paid during the period for income taxes $</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -8368,11 +8116,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H57" s="5" t="n">
-        <v>-0.044945</v>
-      </c>
-      <c r="I57" s="5" t="n">
-        <v>0.476051</v>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -8396,14 +8148,10 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Non-cash transactions</t>
-        </is>
-      </c>
+      <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Common shares issued for debt settlement $</t>
+          <t>October 31, 2023 October</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
@@ -8428,12 +8176,10 @@
         </is>
       </c>
       <c r="I58" s="5" t="n">
-        <v>0.180422</v>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002022</v>
+      </c>
+      <c r="J58" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -8454,15 +8200,19 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Non-cash transactions</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Shares issued for property $</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>Net cash flows used in financing activities</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
           <t>-</t>
@@ -8484,7 +8234,7 @@
         </is>
       </c>
       <c r="I59" s="5" t="n">
-        <v>0.039</v>
+        <v>0.476051</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -8510,12 +8260,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Non-cash transactions</t>
+          <t>Non cash transactions</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cash paid during the year for interest $</t>
+          <t>Share issued for property $</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -8539,10 +8289,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I60" s="5" t="n">
+        <v>0.039</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -8568,12 +8316,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Non-cash transactions</t>
+          <t>Non cash transactions</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Cash paid during the year for income taxes $</t>
+          <t>Cash paid during the year for interest $</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
@@ -8624,10 +8372,14 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Non cash transactions</t>
+        </is>
+      </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>For the year November</t>
+          <t>Cash paid during the year for income taxes $</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
@@ -8636,11 +8388,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F62" s="5" t="n">
-        <v>0.002017</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>2.8e-05</v>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -8676,15 +8432,19 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Adjustments for non-cash items</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Impairmnent</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
+          <t>Prepaid expenses and deposit</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -8695,18 +8455,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G63" s="5" t="n">
-        <v>0.187798</v>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I63" s="5" t="n">
+        <v>-0.126607</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -8732,12 +8492,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Adjustments for non-cash items</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Accrued interest expense</t>
+          <t>Deferred financing fees</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
@@ -8751,13 +8511,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G64" s="5" t="n">
-        <v>8.2e-05</v>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="n">
+        <v>-0.07975500000000001</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -8788,15 +8548,19 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Cash assumed from acquisition of subsidiary</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>Net cash flows provided by (used in) financing activities</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -8807,18 +8571,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G65" s="5" t="n">
-        <v>0.007081</v>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H65" s="5" t="n">
+        <v>-0.044945</v>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>0.476051</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -8844,12 +8606,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Financing activities</t>
+          <t>Non-cash transactions</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Loans advanced</t>
+          <t>Common shares issued for debt settlement $</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
@@ -8863,18 +8625,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G66" s="5" t="n">
-        <v>0.119559</v>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I66" s="5" t="n">
+        <v>0.180422</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -8900,12 +8662,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Non cash transactions</t>
+          <t>Non-cash transactions</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Common shares issued for acquisition of subsidiary</t>
+          <t>Shares issued for property $</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
@@ -8919,18 +8681,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G67" s="5" t="n">
-        <v>0.088972</v>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I67" s="5" t="n">
+        <v>0.039</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -8956,12 +8718,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Non cash transactions</t>
+          <t>Non-cash transactions</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Common shares issued for debt settlement</t>
+          <t>Cash paid during the year for interest $</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
@@ -8970,11 +8732,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F68" s="5" t="n">
-        <v>0.00625</v>
-      </c>
-      <c r="G68" s="5" t="n">
-        <v>0.216514</v>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -9010,12 +8776,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Non cash transactions</t>
+          <t>Non-cash transactions</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Common shares issued under plan of arrangement</t>
+          <t>Cash paid during the year for income taxes $</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
@@ -9024,8 +8790,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F69" s="5" t="n">
-        <v>0.001</v>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -9061,13 +8829,13 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Note October 31, 2025 October</t>
+          <t>For the year November</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -9076,15 +8844,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F70" s="5" t="n">
+        <v>0.002017</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>2.8e-05</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -9101,27 +8865,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K70" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="L70" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Adjustments for non-cash items</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Administration $</t>
+          <t>Impairmnent</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
@@ -9136,45 +8904,51 @@
         </is>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.01524</v>
-      </c>
-      <c r="H71" s="5" t="n">
-        <v>0.031864</v>
-      </c>
-      <c r="I71" s="5" t="n">
-        <v>0.050153</v>
-      </c>
-      <c r="J71" s="5" t="n">
-        <v>0.038099</v>
-      </c>
-      <c r="K71" s="5" t="n">
-        <v>0.03807</v>
-      </c>
-      <c r="L71" s="5" t="n">
-        <v>0.038808</v>
+        <v>0.187798</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Adjustments for non-cash items</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Filing fees</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Accrued interest expense</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -9185,10 +8959,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G72" s="5" t="n">
+        <v>8.2e-05</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -9205,34 +8977,34 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K72" s="5" t="n">
-        <v>0.012363</v>
-      </c>
-      <c r="L72" s="5" t="n">
-        <v>0.014575</v>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Management and consulting fees 6</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Cash assumed from acquisition of subsidiary</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -9243,10 +9015,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G73" s="5" t="n">
+        <v>0.007081</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -9258,126 +9028,148 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J73" s="5" t="n">
-        <v>0.363994</v>
-      </c>
-      <c r="K73" s="5" t="n">
-        <v>0.345092</v>
-      </c>
-      <c r="L73" s="5" t="n">
-        <v>0.366299</v>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Loans advanced</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F74" s="5" t="n">
-        <v>0.0035</v>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.011569</v>
-      </c>
-      <c r="H74" s="5" t="n">
-        <v>0.034792</v>
-      </c>
-      <c r="I74" s="5" t="n">
-        <v>0.031412</v>
-      </c>
-      <c r="J74" s="5" t="n">
-        <v>0.015337</v>
-      </c>
-      <c r="K74" s="5" t="n">
-        <v>0.012598</v>
-      </c>
-      <c r="L74" s="5" t="n">
-        <v>0.01752</v>
+        <v>0.119559</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Non cash transactions</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Total expenses</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
+          <t>Common shares issued for acquisition of subsidiary</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F75" s="5" t="n">
-        <v>0.029312</v>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.571368</v>
-      </c>
-      <c r="H75" s="5" t="n">
-        <v>0.16293</v>
-      </c>
-      <c r="I75" s="5" t="n">
-        <v>0.346661</v>
-      </c>
-      <c r="J75" s="5" t="n">
-        <v>0.51534</v>
-      </c>
-      <c r="K75" s="5" t="n">
-        <v>0.408123</v>
-      </c>
-      <c r="L75" s="5" t="n">
-        <v>0.437202</v>
+        <v>0.088972</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Other Item</t>
+          <t>Non cash transactions</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Gain on forgiveness of debts $</t>
+          <t>Common shares issued for debt settlement</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
@@ -9386,15 +9178,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F76" s="5" t="n">
+        <v>0.00625</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>0.216514</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -9416,24 +9204,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L76" s="5" t="n">
-        <v>0.220436</v>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Other Item</t>
+          <t>Non cash transactions</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Total other item</t>
+          <t>Common shares issued under plan of arrangement</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
@@ -9442,10 +9232,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F77" s="5" t="n">
+        <v>0.001</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -9472,8 +9260,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="L77" s="5" t="n">
-        <v>0.220436</v>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -9482,21 +9272,13 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Other Item</t>
-        </is>
-      </c>
+      <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Net loss $</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Note October 31, 2025 October</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -9528,10 +9310,10 @@
         </is>
       </c>
       <c r="K78" s="5" t="n">
-        <v>-0.408123</v>
+        <v>0.002024</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>-0.216766</v>
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="79">
@@ -9542,46 +9324,42 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Other Item</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Administration $</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F79" s="5" t="n">
-        <v>-0.029312</v>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G79" s="5" t="n">
-        <v>-0.759248</v>
+        <v>0.01524</v>
       </c>
       <c r="H79" s="5" t="n">
-        <v>-0.16908</v>
+        <v>0.031864</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>-0.346661</v>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.050153</v>
+      </c>
+      <c r="J79" s="5" t="n">
+        <v>0.038099</v>
       </c>
       <c r="K79" s="5" t="n">
-        <v>-0.408123</v>
+        <v>0.03807</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>-0.216766</v>
+        <v>0.038808</v>
       </c>
     </row>
     <row r="80">
@@ -9592,17 +9370,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share $</t>
+          <t>Filing fees</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -9636,10 +9414,10 @@
         </is>
       </c>
       <c r="K80" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.012363</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>0</v>
+        <v>0.014575</v>
       </c>
     </row>
     <row r="81">
@@ -9650,17 +9428,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Weighted average and fully diluted</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Weighted average and fully diluted common shares outstanding</t>
+          <t>Management and consulting fees 6</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -9683,17 +9461,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I81" s="5" t="n">
-        <v>38.446784</v>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J81" s="5" t="n">
-        <v>44.730338</v>
+        <v>0.363994</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>44.730338</v>
+        <v>0.345092</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>59.358737</v>
+        <v>0.366299</v>
       </c>
     </row>
     <row r="82">
@@ -9704,50 +9484,44 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Number   Share Capital    Reserves        Deficit        Total</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Balance at October 31, 2023 44,730,338 $ 2,524,443 $ 24,643 $</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E82" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F82" s="5" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>0.011569</v>
+      </c>
+      <c r="H82" s="5" t="n">
+        <v>0.034792</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>0.031412</v>
+      </c>
+      <c r="J82" s="5" t="n">
+        <v>0.015337</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>0.5783239999999999</v>
+        <v>0.012598</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>-1.970762</v>
+        <v>0.01752</v>
       </c>
     </row>
     <row r="83">
@@ -9758,17 +9532,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Number   Share Capital    Reserves        Deficit        Total</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Loss for the year - - -</t>
+          <t>Total expenses</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -9776,36 +9550,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F83" s="5" t="n">
+        <v>0.029312</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>0.571368</v>
+      </c>
+      <c r="H83" s="5" t="n">
+        <v>0.16293</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>0.346661</v>
+      </c>
+      <c r="J83" s="5" t="n">
+        <v>0.51534</v>
       </c>
       <c r="K83" s="5" t="n">
-        <v>-0.408123</v>
+        <v>0.408123</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>-0.408123</v>
+        <v>0.437202</v>
       </c>
     </row>
     <row r="84">
@@ -9816,12 +9580,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Number   Share Capital    Reserves        Deficit        Total</t>
+          <t>Other Item</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Balance at October 31, 2024 44,730,338 $ 2,524,443 $ 24,643 $</t>
+          <t>Gain on forgiveness of debts $</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
@@ -9855,11 +9619,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K84" s="5" t="n">
-        <v>0.170201</v>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L84" s="5" t="n">
-        <v>-2.378885</v>
+        <v>0.220436</v>
       </c>
     </row>
     <row r="85">
@@ -9870,12 +9636,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Number   Share Capital    Reserves        Deficit        Total</t>
+          <t>Other Item</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Share issued for private placement 34,721,727 1,412,836 -</t>
+          <t>Total other item</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
@@ -9909,13 +9675,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K85" s="5" t="n">
-        <v>1.412836</v>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>0.220436</v>
       </c>
     </row>
     <row r="86">
@@ -9926,15 +9692,19 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Number   Share Capital    Reserves        Deficit        Total</t>
+          <t>Other Item</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Share issued for debt settlement 4,750,000 95,000 -</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
+          <t>Net loss $</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
           <t>-</t>
@@ -9966,12 +9736,10 @@
         </is>
       </c>
       <c r="K86" s="5" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.408123</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>-0.216766</v>
       </c>
     </row>
     <row r="87">
@@ -9982,39 +9750,35 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Number   Share Capital    Reserves        Deficit        Total</t>
+          <t>Other Item</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Share issuance costs - (60,950) 21,301</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
+          <t>Loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F87" s="5" t="n">
+        <v>-0.029312</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>-0.759248</v>
+      </c>
+      <c r="H87" s="5" t="n">
+        <v>-0.16908</v>
+      </c>
+      <c r="I87" s="5" t="n">
+        <v>-0.346661</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -10022,12 +9786,10 @@
         </is>
       </c>
       <c r="K87" s="5" t="n">
-        <v>-0.039649</v>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.408123</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>-0.216766</v>
       </c>
     </row>
     <row r="88">
@@ -10038,15 +9800,19 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Number   Share Capital    Reserves        Deficit        Total</t>
+          <t>Basic and diluted loss per common</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Balance at October 31, 2025 84,202,065 $ 3,971,329 $ 45,944 $</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
+          <t>Basic and diluted loss per common share $</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -10078,10 +9844,10 @@
         </is>
       </c>
       <c r="K88" s="5" t="n">
-        <v>1.421622</v>
+        <v>-1e-08</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>-2.595651</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -10090,13 +9856,21 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Weighted average and fully diluted</t>
+        </is>
+      </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Note October 31, 2024 October</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
+          <t>Weighted average and fully diluted common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -10117,21 +9891,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I89" s="5" t="n">
+        <v>38.446784</v>
       </c>
       <c r="J89" s="5" t="n">
-        <v>0.002023</v>
+        <v>44.730338</v>
       </c>
       <c r="K89" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>44.730338</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>59.358737</v>
       </c>
     </row>
     <row r="90">
@@ -10142,12 +9912,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Number   Share Capital    Reserves        Deficit        Total</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Marketing costs</t>
+          <t>Balance at October 31, 2023 44,730,338 $ 2,524,443 $ 24,643 $</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
@@ -10171,21 +9941,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I90" s="5" t="n">
-        <v>0.08550000000000001</v>
-      </c>
-      <c r="J90" s="5" t="n">
-        <v>0.08550000000000001</v>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>0.5783239999999999</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>-1.970762</v>
       </c>
     </row>
     <row r="91">
@@ -10196,17 +9966,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Number   Share Capital    Reserves        Deficit        Total</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Listing and filing fees</t>
+          <t>Loss for the year - - -</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -10214,28 +9984,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F91" s="5" t="n">
-        <v>0.000195</v>
-      </c>
-      <c r="G91" s="5" t="n">
-        <v>0.089281</v>
-      </c>
-      <c r="H91" s="5" t="n">
-        <v>0.003545</v>
-      </c>
-      <c r="I91" s="5" t="n">
-        <v>0.0224</v>
-      </c>
-      <c r="J91" s="5" t="n">
-        <v>0.01241</v>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K91" s="5" t="n">
-        <v>0.012363</v>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.408123</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>-0.408123</v>
       </c>
     </row>
     <row r="92">
@@ -10246,19 +10024,15 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Number   Share Capital    Reserves        Deficit        Total</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Loss and comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Balance at October 31, 2024 44,730,338 $ 2,524,443 $ 24,643 $</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
           <t>-</t>
@@ -10279,19 +10053,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I92" s="5" t="n">
-        <v>-0.346661</v>
-      </c>
-      <c r="J92" s="5" t="n">
-        <v>-0.51534</v>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K92" s="5" t="n">
-        <v>-0.408123</v>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.170201</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>-2.378885</v>
       </c>
     </row>
     <row r="93">
@@ -10302,19 +10078,15 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Number   Share Capital    Reserves        Deficit        Total</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share $</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Share issued for private placement 34,721,727 1,412,836 -</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -10335,14 +10107,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I93" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="J93" s="5" t="n">
-        <v>-1e-08</v>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K93" s="5" t="n">
-        <v>-1e-08</v>
+        <v>1.412836</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -10358,12 +10134,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Number   Share Capital      Reserves            Deficit         Total</t>
+          <t>Number   Share Capital    Reserves        Deficit        Total</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Balance at October 31, 2022 44,730,338 $ 2,524,443 $ 24,643 $</t>
+          <t>Share issued for debt settlement 4,750,000 95,000 -</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
@@ -10392,11 +10168,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J94" s="5" t="n">
-        <v>1.093664</v>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K94" s="5" t="n">
-        <v>-1.455422</v>
+        <v>0.095</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -10412,19 +10190,15 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Number   Share Capital      Reserves            Deficit         Total</t>
+          <t>Number   Share Capital    Reserves        Deficit        Total</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Share issuance costs - (60,950) 21,301</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
           <t>-</t>
@@ -10450,11 +10224,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J95" s="5" t="n">
-        <v>-0.51534</v>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K95" s="5" t="n">
-        <v>-0.51534</v>
+        <v>-0.039649</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -10470,12 +10246,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Number   Share Capital      Reserves            Deficit         Total</t>
+          <t>Number   Share Capital    Reserves        Deficit        Total</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Balance at October 31, 2023 44,730,338 $ 2,524,443 $ 24,643 $</t>
+          <t>Balance at October 31, 2025 84,202,065 $ 3,971,329 $ 45,944 $</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
@@ -10504,16 +10280,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J96" s="5" t="n">
-        <v>0.5783239999999999</v>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K96" s="5" t="n">
-        <v>-1.970762</v>
-      </c>
-      <c r="L96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.421622</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>-2.595651</v>
       </c>
     </row>
     <row r="97">
@@ -10522,14 +10298,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Number   Share Capital      Reserves            Deficit         Total</t>
-        </is>
-      </c>
+      <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Balance at October 31, 2024 44,730,338 $ 2,524,443 $ 24,643 $</t>
+          <t>Note October 31, 2024 October</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
@@ -10559,10 +10331,10 @@
         </is>
       </c>
       <c r="J97" s="5" t="n">
-        <v>0.170201</v>
+        <v>0.002023</v>
       </c>
       <c r="K97" s="5" t="n">
-        <v>-2.378885</v>
+        <v>3.1e-05</v>
       </c>
       <c r="L97" t="inlineStr">
         <is>
@@ -10576,10 +10348,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Operating Expenses</t>
+        </is>
+      </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>October 31, 2023 October</t>
+          <t>Marketing costs</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
@@ -10604,10 +10380,10 @@
         </is>
       </c>
       <c r="I98" s="5" t="n">
-        <v>0.002022</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="J98" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -10633,12 +10409,12 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Management and consulting fees</t>
+          <t>Listing and filing fees</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -10646,29 +10422,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F99" s="5" t="n">
+        <v>0.000195</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>0.089281</v>
       </c>
       <c r="H99" s="5" t="n">
-        <v>0.09272900000000001</v>
+        <v>0.003545</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>0.157196</v>
+        <v>0.0224</v>
       </c>
       <c r="J99" s="5" t="n">
-        <v>0.363994</v>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.01241</v>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>0.012363</v>
       </c>
       <c r="L99" t="inlineStr">
         <is>
@@ -10684,15 +10454,19 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Number   Share Capital      Reserves          Deficit          Total</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Shares issued for cash 6,500,000</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr"/>
+          <t>Loss and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E100" t="inlineStr">
         <is>
           <t>-</t>
@@ -10714,15 +10488,13 @@
         </is>
       </c>
       <c r="I100" s="5" t="n">
-        <v>0.65</v>
+        <v>-0.346661</v>
       </c>
       <c r="J100" s="5" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.51534</v>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v>-0.408123</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -10738,15 +10510,19 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Number   Share Capital      Reserves          Deficit          Total</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Shares issued-debt settlement 1,804,218 180,422 -</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
+          <t>Basic and diluted loss per common share $</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -10768,17 +10544,13 @@
         </is>
       </c>
       <c r="I101" s="5" t="n">
-        <v>0.180422</v>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1e-08</v>
+      </c>
+      <c r="J101" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -10794,12 +10566,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Number   Share Capital      Reserves          Deficit          Total</t>
+          <t>Number   Share Capital      Reserves            Deficit         Total</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Shares issued for property 300,000 39,000 -</t>
+          <t>Balance at October 31, 2022 44,730,338 $ 2,524,443 $ 24,643 $</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
@@ -10823,18 +10595,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I102" s="5" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J102" s="5" t="n">
+        <v>1.093664</v>
+      </c>
+      <c r="K102" s="5" t="n">
+        <v>-1.455422</v>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -10850,15 +10620,19 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Number   Share Capital      Reserves          Deficit          Total</t>
+          <t>Number   Share Capital      Reserves            Deficit         Total</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Share issuance costs - (310,906) 24,643</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
+          <t>Loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E103" t="inlineStr">
         <is>
           <t>-</t>
@@ -10879,18 +10653,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I103" s="5" t="n">
-        <v>-0.286263</v>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J103" s="5" t="n">
+        <v>-0.51534</v>
+      </c>
+      <c r="K103" s="5" t="n">
+        <v>-0.51534</v>
       </c>
       <c r="L103" t="inlineStr">
         <is>
@@ -10906,19 +10678,15 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Number   Share Capital      Reserves          Deficit          Total</t>
+          <t>Number   Share Capital      Reserves            Deficit         Total</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Balance at October 31, 2023 44,730,338 $ 2,524,443 $ 24,643 $</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -10939,16 +10707,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I104" s="5" t="n">
-        <v>-0.346661</v>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J104" s="5" t="n">
-        <v>-0.346661</v>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.5783239999999999</v>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>-1.970762</v>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -10964,12 +10732,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Other Item</t>
+          <t>Number   Share Capital      Reserves            Deficit         Total</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Write-off of GST receivable</t>
+          <t>Balance at October 31, 2024 44,730,338 $ 2,524,443 $ 24,643 $</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
@@ -10988,23 +10756,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H105" s="5" t="n">
-        <v>-0.00615</v>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J105" s="5" t="n">
+        <v>0.170201</v>
+      </c>
+      <c r="K105" s="5" t="n">
+        <v>-2.378885</v>
       </c>
       <c r="L105" t="inlineStr">
         <is>
@@ -11018,42 +10784,38 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Other Item</t>
-        </is>
-      </c>
+      <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share $</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>October 31, 2023 October</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F106" s="5" t="n">
-        <v>-2.5e-07</v>
-      </c>
-      <c r="G106" s="5" t="n">
-        <v>-5e-08</v>
-      </c>
-      <c r="H106" s="5" t="n">
-        <v>0</v>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I106" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002022</v>
+      </c>
+      <c r="J106" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
@@ -11074,17 +10836,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Weighted average and fully diluted common shares</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Weighted average and fully diluted common shares outstanding</t>
+          <t>Management and consulting fees</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -11092,22 +10854,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F107" s="5" t="n">
-        <v>0.119333</v>
-      </c>
-      <c r="G107" s="5" t="n">
-        <v>15.0896</v>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H107" s="5" t="n">
-        <v>35.875161</v>
+        <v>0.09272900000000001</v>
       </c>
       <c r="I107" s="5" t="n">
-        <v>38.446784</v>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.157196</v>
+      </c>
+      <c r="J107" s="5" t="n">
+        <v>0.363994</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
@@ -11128,12 +10892,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Number  Share Capital    Reserves        Deficit         Total</t>
+          <t>Number   Share Capital      Reserves          Deficit          Total</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Balance at October 31, 2020 35,726,120 $ 1,931,117 $ - $</t>
+          <t>Shares issued for cash 6,500,000</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
@@ -11152,16 +10916,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H108" s="5" t="n">
-        <v>0.991436</v>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I108" s="5" t="n">
-        <v>-0.939681</v>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.65</v>
+      </c>
+      <c r="J108" s="5" t="n">
+        <v>0.65</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
@@ -11182,12 +10946,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Number  Share Capital    Reserves        Deficit         Total</t>
+          <t>Number   Share Capital      Reserves          Deficit          Total</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Share issuance costs - (5,190) -</t>
+          <t>Shares issued-debt settlement 1,804,218 180,422 -</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
@@ -11206,13 +10970,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H109" s="5" t="n">
-        <v>-0.00519</v>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I109" s="5" t="n">
+        <v>0.180422</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -11238,12 +11002,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Number  Share Capital    Reserves        Deficit         Total</t>
+          <t>Number   Share Capital      Reserves          Deficit          Total</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Shares issued for cash 400,000 40,000 -</t>
+          <t>Shares issued for property 300,000 39,000 -</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
@@ -11262,13 +11026,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H110" s="5" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I110" s="5" t="n">
+        <v>0.039</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -11294,19 +11058,15 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Number  Share Capital    Reserves        Deficit         Total</t>
+          <t>Number   Share Capital      Reserves          Deficit          Total</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Share issuance costs - (310,906) 24,643</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -11322,11 +11082,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H111" s="5" t="n">
-        <v>-0.16908</v>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I111" s="5" t="n">
-        <v>-0.16908</v>
+        <v>-0.286263</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -11352,15 +11114,19 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Number  Share Capital    Reserves        Deficit         Total</t>
+          <t>Number   Share Capital      Reserves          Deficit          Total</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Balance at October 31, 2021 36,126,120 $ 1,965,927 $ - $</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr"/>
+          <t>Loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
@@ -11376,16 +11142,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H112" s="5" t="n">
-        <v>0.857166</v>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I112" s="5" t="n">
-        <v>-1.108761</v>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.346661</v>
+      </c>
+      <c r="J112" s="5" t="n">
+        <v>-0.346661</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
@@ -11406,12 +11172,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Number  Share Capital    Reserves        Deficit         Total</t>
+          <t>Other Item</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Shares issued for cash 6,500,000 $ 650,000 -</t>
+          <t>Write-off of GST receivable</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
@@ -11431,7 +11197,7 @@
         </is>
       </c>
       <c r="H113" s="5" t="n">
-        <v>0.65</v>
+        <v>-0.00615</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -11462,37 +11228,35 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Shares issued for debt</t>
+          <t>Other Item</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Shares issued for debt settlement 1,804,218 180,422 -</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr"/>
+          <t>Basic and diluted loss per common share $</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F114" s="5" t="n">
+        <v>-2.5e-07</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>-5e-08</v>
       </c>
       <c r="H114" s="5" t="n">
-        <v>0.180422</v>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="I114" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -11518,37 +11282,35 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Shares issued for debt</t>
+          <t>Weighted average and fully diluted common shares</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Shares issued for property 300,000 39,000 -</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
+          <t>Weighted average and fully diluted common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F115" s="5" t="n">
+        <v>0.119333</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>15.0896</v>
       </c>
       <c r="H115" s="5" t="n">
-        <v>0.039</v>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>35.875161</v>
+      </c>
+      <c r="I115" s="5" t="n">
+        <v>38.446784</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -11574,12 +11336,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Shares issued for debt</t>
+          <t>Number  Share Capital    Reserves        Deficit         Total</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Share issuance costs - (310,906) 24,643</t>
+          <t>Balance at October 31, 2020 35,726,120 $ 1,931,117 $ - $</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
@@ -11599,12 +11361,10 @@
         </is>
       </c>
       <c r="H116" s="5" t="n">
-        <v>-0.286263</v>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.991436</v>
+      </c>
+      <c r="I116" s="5" t="n">
+        <v>-0.939681</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -11630,19 +11390,15 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Shares issued for debt</t>
+          <t>Number  Share Capital    Reserves        Deficit         Total</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Share issuance costs - (5,190) -</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -11659,10 +11415,12 @@
         </is>
       </c>
       <c r="H117" s="5" t="n">
-        <v>-0.346661</v>
-      </c>
-      <c r="I117" s="5" t="n">
-        <v>-0.346661</v>
+        <v>-0.00519</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -11688,12 +11446,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Shares issued for debt</t>
+          <t>Number  Share Capital    Reserves        Deficit         Total</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Balance at October 31, 2022 44,730,338 $ 2,524,443 $ 24,643 $</t>
+          <t>Shares issued for cash 400,000 40,000 -</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -11713,10 +11471,12 @@
         </is>
       </c>
       <c r="H118" s="5" t="n">
-        <v>1.093664</v>
-      </c>
-      <c r="I118" s="5" t="n">
-        <v>-1.455422</v>
+        <v>0.04</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -11740,33 +11500,41 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr"/>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Number  Share Capital    Reserves        Deficit         Total</t>
+        </is>
+      </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>November</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr"/>
+          <t>Loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F119" s="5" t="n">
-        <v>0.002017</v>
-      </c>
-      <c r="G119" s="5" t="n">
-        <v>2.8e-05</v>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H119" s="5" t="n">
+        <v>-0.16908</v>
+      </c>
+      <c r="I119" s="5" t="n">
+        <v>-0.16908</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -11792,39 +11560,35 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Number  Share Capital    Reserves        Deficit         Total</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Management and consulting fees 8</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Balance at October 31, 2021 36,126,120 $ 1,965,927 $ - $</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F120" s="5" t="n">
-        <v>0.025617</v>
-      </c>
-      <c r="G120" s="5" t="n">
-        <v>0.080278</v>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H120" s="5" t="n">
+        <v>0.857166</v>
+      </c>
+      <c r="I120" s="5" t="n">
+        <v>-1.108761</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -11850,12 +11614,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Number  Share Capital    Reserves        Deficit         Total</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Property evaluation 8</t>
+          <t>Shares issued for cash 6,500,000 $ 650,000 -</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
@@ -11869,13 +11633,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G121" s="5" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H121" s="5" t="n">
+        <v>0.65</v>
       </c>
       <c r="I121" t="inlineStr">
         <is>
@@ -11906,12 +11670,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Other Item</t>
+          <t>Shares issued for debt</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Impairment 4</t>
+          <t>Shares issued for debt settlement 1,804,218 180,422 -</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -11925,13 +11689,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G122" s="5" t="n">
-        <v>-0.187798</v>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H122" s="5" t="n">
+        <v>0.180422</v>
       </c>
       <c r="I122" t="inlineStr">
         <is>
@@ -11962,19 +11726,15 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Other Item</t>
+          <t>Shares issued for debt</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Interest expense 6</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>InterestExpenseOperating</t>
-        </is>
-      </c>
+          <t>Shares issued for property 300,000 39,000 -</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -11985,13 +11745,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G123" s="5" t="n">
-        <v>-8.2e-05</v>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H123" s="5" t="n">
+        <v>0.039</v>
       </c>
       <c r="I123" t="inlineStr">
         <is>
@@ -12022,12 +11782,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Note        Number         Share Capital                Deficit                 Total</t>
+          <t>Shares issued for debt</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>November 28, 2017 (date of inception) - $ - $</t>
+          <t>Share issuance costs - (310,906) 24,643</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
@@ -12046,10 +11806,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H124" s="5" t="n">
+        <v>-0.286263</v>
       </c>
       <c r="I124" t="inlineStr">
         <is>
@@ -12080,37 +11838,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Note        Number         Share Capital                Deficit                 Total</t>
+          <t>Shares issued for debt</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Incorporator shares 100 1</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr"/>
+          <t>Loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E125" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F125" s="5" t="n">
-        <v>1e-06</v>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H125" s="5" t="n">
+        <v>-0.346661</v>
+      </c>
+      <c r="I125" s="5" t="n">
+        <v>-0.346661</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -12136,12 +11896,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Note        Number         Share Capital                Deficit                 Total</t>
+          <t>Shares issued for debt</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Cancellation of incorporator shares (100) (1)</t>
+          <t>Balance at October 31, 2022 44,730,338 $ 2,524,443 $ 24,643 $</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -12150,23 +11910,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F126" s="5" t="n">
-        <v>-1e-06</v>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H126" s="5" t="n">
+        <v>1.093664</v>
+      </c>
+      <c r="I126" s="5" t="n">
+        <v>-1.455422</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -12190,14 +11948,10 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Note        Number         Share Capital                Deficit                 Total</t>
-        </is>
-      </c>
+      <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Shares reserved for issuance under plan of arrangement 12 855,400 1,000</t>
+          <t>November</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
@@ -12207,12 +11961,10 @@
         </is>
       </c>
       <c r="F127" s="5" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002017</v>
+      </c>
+      <c r="G127" s="5" t="n">
+        <v>2.8e-05</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
@@ -12248,27 +12000,29 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Note        Number         Share Capital                Deficit                 Total</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Shares issued, under debt settlement agreement 7 1,250,000 6,250</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
+          <t>Management and consulting fees 8</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F128" s="5" t="n">
-        <v>0.00625</v>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.025617</v>
+      </c>
+      <c r="G128" s="5" t="n">
+        <v>0.080278</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
@@ -12304,29 +12058,27 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Note        Number         Share Capital                Deficit                 Total</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Loss for the period - -</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Property evaluation 8</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F129" s="5" t="n">
-        <v>-0.029312</v>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G129" s="5" t="n">
-        <v>-0.029312</v>
+        <v>0.375</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -12362,12 +12114,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Note        Number         Share Capital                Deficit                 Total</t>
+          <t>Other Item</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Balance at October 31, 2018 2,105,400 $ 7,250 $</t>
+          <t>Impairment 4</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
@@ -12376,11 +12128,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F130" s="5" t="n">
-        <v>-0.022062</v>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G130" s="5" t="n">
-        <v>-0.029312</v>
+        <v>-0.187798</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -12416,25 +12170,31 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Note        Number         Share Capital                Deficit                 Total</t>
+          <t>Other Item</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Balance at October 31, 2018 2,105,400 7,250</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
+          <t>Interest expense 6</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F131" s="5" t="n">
-        <v>-0.022062</v>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G131" s="5" t="n">
-        <v>-0.029312</v>
+        <v>-8.2e-05</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -12475,7 +12235,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Shares issued, under debt settlement agreement 7 12,325,700 216,514</t>
+          <t>November 28, 2017 (date of inception) - $ - $</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
@@ -12484,8 +12244,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F132" s="5" t="n">
-        <v>0.216514</v>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -12531,7 +12293,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Shares issued, acquisition of subsidiary 3,7 5,065,020 88,972</t>
+          <t>Incorporator shares 100 1</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
@@ -12541,7 +12303,7 @@
         </is>
       </c>
       <c r="F133" s="5" t="n">
-        <v>0.088972</v>
+        <v>1e-06</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -12587,24 +12349,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Loss for the year - -</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Cancellation of incorporator shares (100) (1)</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F134" s="5" t="n">
-        <v>-0.759248</v>
-      </c>
-      <c r="G134" s="5" t="n">
-        <v>-0.759248</v>
+        <v>-1e-06</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -12645,7 +12405,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Balance at October 31, 2019 19,496,120 $ 312,736 $</t>
+          <t>Shares reserved for issuance under plan of arrangement 12 855,400 1,000</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
@@ -12655,32 +12415,480 @@
         </is>
       </c>
       <c r="F135" s="5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Note        Number         Share Capital                Deficit                 Total</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Shares issued, under debt settlement agreement 7 1,250,000 6,250</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F136" s="5" t="n">
+        <v>0.00625</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Note        Number         Share Capital                Deficit                 Total</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Loss for the period - -</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F137" s="5" t="n">
+        <v>-0.029312</v>
+      </c>
+      <c r="G137" s="5" t="n">
+        <v>-0.029312</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Note        Number         Share Capital                Deficit                 Total</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Balance at October 31, 2018 2,105,400 $ 7,250 $</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F138" s="5" t="n">
+        <v>-0.022062</v>
+      </c>
+      <c r="G138" s="5" t="n">
+        <v>-0.029312</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Note        Number         Share Capital                Deficit                 Total</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Balance at October 31, 2018 2,105,400 7,250</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F139" s="5" t="n">
+        <v>-0.022062</v>
+      </c>
+      <c r="G139" s="5" t="n">
+        <v>-0.029312</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Note        Number         Share Capital                Deficit                 Total</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Shares issued, under debt settlement agreement 7 12,325,700 216,514</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F140" s="5" t="n">
+        <v>0.216514</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Note        Number         Share Capital                Deficit                 Total</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Shares issued, acquisition of subsidiary 3,7 5,065,020 88,972</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F141" s="5" t="n">
+        <v>0.088972</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Note        Number         Share Capital                Deficit                 Total</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Loss for the year - -</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F142" s="5" t="n">
+        <v>-0.759248</v>
+      </c>
+      <c r="G142" s="5" t="n">
+        <v>-0.759248</v>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Note        Number         Share Capital                Deficit                 Total</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Balance at October 31, 2019 19,496,120 $ 312,736 $</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F143" s="5" t="n">
         <v>-0.475824</v>
       </c>
-      <c r="G135" s="5" t="n">
+      <c r="G143" s="5" t="n">
         <v>-0.78856</v>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L135" t="inlineStr">
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
         <is>
           <t>-</t>
         </is>
